--- a/RevitMappingData/ProjectNamingMatrix.xlsx
+++ b/RevitMappingData/ProjectNamingMatrix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\source\repos\NewDigitalDelivery\DigitalDelivery\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZAMORAMARIACARLOTAGA\Documents\GitHub\pocDataRepo\RevitMappingData\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{2372C078-2398-4E8A-85B9-1FF81B27CFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9201FB46-1EFA-4E55-9FE4-80AD54258EB1}"/>
   <bookViews>
-    <workbookView xWindow="29850" yWindow="-14730" windowWidth="30780" windowHeight="11235" xr2:uid="{D777F439-9358-4388-BAEA-A8A675FE2155}"/>
+    <workbookView xWindow="21765" yWindow="-14025" windowWidth="26160" windowHeight="11235" xr2:uid="{D777F439-9358-4388-BAEA-A8A675FE2155}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,13 +432,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75A7B1FA-DDB9-4761-BB99-B237A4A10C73}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,7 +449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -460,7 +460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/RevitMappingData/ProjectNamingMatrix.xlsx
+++ b/RevitMappingData/ProjectNamingMatrix.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZAMORAMARIACARLOTAGA\Documents\GitHub\pocDataRepo\RevitMappingData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{2372C078-2398-4E8A-85B9-1FF81B27CFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9201FB46-1EFA-4E55-9FE4-80AD54258EB1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CCF43B-F379-453D-AD27-D8E65DBCA554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21765" yWindow="-14025" windowWidth="26160" windowHeight="11235" xr2:uid="{D777F439-9358-4388-BAEA-A8A675FE2155}"/>
+    <workbookView xWindow="37800" yWindow="-13920" windowWidth="21510" windowHeight="11235" activeTab="1" xr2:uid="{D777F439-9358-4388-BAEA-A8A675FE2155}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="NamingMatrix" sheetId="1" r:id="rId1"/>
+    <sheet name="RiserLibrary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>ItemKey</t>
   </si>
@@ -60,19 +61,71 @@
   </si>
   <si>
     <t>Riser</t>
+  </si>
+  <si>
+    <t>RiserCode</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ELEC</t>
+  </si>
+  <si>
+    <t>Electrical Riser</t>
+  </si>
+  <si>
+    <t>CHWR</t>
+  </si>
+  <si>
+    <t>Chilled Water Riser</t>
+  </si>
+  <si>
+    <t>ELV</t>
+  </si>
+  <si>
+    <t>Extra Low Voltage</t>
+  </si>
+  <si>
+    <t>TEL</t>
+  </si>
+  <si>
+    <t>Telecommunications</t>
+  </si>
+  <si>
+    <t>PS</t>
+  </si>
+  <si>
+    <t>Pipe Sleeve / Plumbing</t>
+  </si>
+  <si>
+    <t>EAD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -95,8 +148,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,4 +539,71 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF73498-A899-41FA-BFDB-8FB404F3D88D}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/RevitMappingData/ProjectNamingMatrix.xlsx
+++ b/RevitMappingData/ProjectNamingMatrix.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZAMORAMARIACARLOTAGA\Documents\GitHub\pocDataRepo\RevitMappingData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CCF43B-F379-453D-AD27-D8E65DBCA554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D258E4C-B4AC-44D0-B974-62771677AC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37800" yWindow="-13920" windowWidth="21510" windowHeight="11235" activeTab="1" xr2:uid="{D777F439-9358-4388-BAEA-A8A675FE2155}"/>
+    <workbookView xWindow="19080" yWindow="-15615" windowWidth="21510" windowHeight="11235" xr2:uid="{D777F439-9358-4388-BAEA-A8A675FE2155}"/>
   </bookViews>
   <sheets>
     <sheet name="NamingMatrix" sheetId="1" r:id="rId1"/>
     <sheet name="RiserLibrary" sheetId="2" r:id="rId2"/>
+    <sheet name="ClearanceRequirement" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>ItemKey</t>
   </si>
@@ -100,6 +101,36 @@
   </si>
   <si>
     <t>EAD</t>
+  </si>
+  <si>
+    <t>RoomNameFilter</t>
+  </si>
+  <si>
+    <t>MOHH_Width</t>
+  </si>
+  <si>
+    <t>MOHH_Length</t>
+  </si>
+  <si>
+    <t>MOHH_Headroom</t>
+  </si>
+  <si>
+    <t>POC Standard_Width</t>
+  </si>
+  <si>
+    <t>POC Standard_Length</t>
+  </si>
+  <si>
+    <t>POC Standard_Headroom</t>
+  </si>
+  <si>
+    <t>Corridor</t>
+  </si>
+  <si>
+    <t>Lobby</t>
+  </si>
+  <si>
+    <t>Ambulant</t>
   </si>
 </sst>
 </file>
@@ -606,4 +637,127 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45E49513-FEA3-4209-A67A-09EAD999AC15}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2">
+        <v>1200</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>2000</v>
+      </c>
+      <c r="F2">
+        <v>1500</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3">
+        <v>2000</v>
+      </c>
+      <c r="D3">
+        <v>2000</v>
+      </c>
+      <c r="E3">
+        <v>2000</v>
+      </c>
+      <c r="F3">
+        <v>1500</v>
+      </c>
+      <c r="G3">
+        <v>1500</v>
+      </c>
+      <c r="H3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4">
+        <v>1800</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>2000</v>
+      </c>
+      <c r="F4">
+        <v>1200</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>